--- a/rules/CORE-000468/positive/02/data/unit-test-coreid-CG0276-positive 2.xlsx
+++ b/rules/CORE-000468/positive/02/data/unit-test-coreid-CG0276-positive 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QF\CORE\core-contributor\rules\CORE-000468\positive\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D14D07-5B27-4367-B317-806B7018F251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FA354F-4411-4EDD-B2FE-86CC49D3D5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2243,16 +2243,16 @@
       <c r="B46" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="6">
-        <v>1</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>117</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G46" s="6" t="s">
@@ -2275,16 +2275,16 @@
       <c r="B47" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="7">
         <v>2</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="6" t="s">
         <v>119</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G47" s="6" t="s">
@@ -2486,16 +2486,16 @@
       <c r="B55" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="6">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>117</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="5" t="s">
         <v>193</v>
       </c>
       <c r="G55" s="6" t="s">
@@ -2515,16 +2515,16 @@
       <c r="B56" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="7">
         <v>2</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="6" t="s">
         <v>200</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="5" t="s">
         <v>193</v>
       </c>
       <c r="G56" s="6" t="s">
